--- a/data/Soil_Probe_Inventory.xlsx
+++ b/data/Soil_Probe_Inventory.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tacaro/Library/CloudStorage/Box-Box/projects/DroughtSIP/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tacaro/Documents/GitHub/DroughtSIP/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA102E65-D9FE-B443-BA5A-D548FC3F43A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3874E484-B00E-794A-B5AB-52E77AEC21D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15120" yWindow="760" windowWidth="15120" windowHeight="18880" xr2:uid="{ADC685AB-0CD7-164B-B506-5E5139665C97}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="74">
   <si>
     <t>Length</t>
   </si>
@@ -234,6 +234,30 @@
   </si>
   <si>
     <t>DL626</t>
+  </si>
+  <si>
+    <t>LOM - ROS</t>
+  </si>
+  <si>
+    <t>TMS 95258424</t>
+  </si>
+  <si>
+    <t>TMS 9523667</t>
+  </si>
+  <si>
+    <t>TMS 95258401</t>
+  </si>
+  <si>
+    <t>TMS 95253672</t>
+  </si>
+  <si>
+    <t>LOM - SKY</t>
+  </si>
+  <si>
+    <t>TMS 95258413</t>
+  </si>
+  <si>
+    <t>TMS 95258434</t>
   </si>
 </sst>
 </file>
@@ -621,7 +645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99388A37-C8FC-344E-A079-CBE2AFBEE4BD}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.1640625" customWidth="1"/>
@@ -905,193 +929,241 @@
         <v>45610</v>
       </c>
     </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" t="s">
+        <v>66</v>
+      </c>
+    </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B25" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E17" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E18" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E19" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E20" s="3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E21" s="3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E22" s="3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E23" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E24" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E25" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E27" s="3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E28" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E29" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E30" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E31" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E32" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E33" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E28" s="3" t="b">
+      <c r="E34" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E35" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E36" s="3" t="b">
         <v>0</v>
       </c>
     </row>
